--- a/feat/migration-contenu-metier/ig/StructureDefinition-fr-lm-result-data.xlsx
+++ b/feat/migration-contenu-metier/ig/StructureDefinition-fr-lm-result-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:07:21+00:00</t>
+    <t>2026-07-16T15:38:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
